--- a/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
+++ b/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\ReframeworkTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23108245-C283-4E79-9CF1-075607133765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9416FC7C-13E9-4FAA-ADCD-EEBCA5873071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,7 +383,7 @@
     <t>{"TO":{"VShort":2, "Short":4, "Medium":16, "Long":64, "VLong":256},
 "TOms":{"VShort":2000, "Short":4000, "Medium":16000, "Long":64000, "VLong":256000},
 "DEL":{"D1":1, "D2":2, "D3":3, "D4":4, "D6":6, "WaitForQueue":45},
-"RS":{"DeleteFiles":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
+"RS":{"DeleteFiles":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":12}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
 "SE":["SE00: Critical error while reading Config file.", 
 "SE01: Critical error while initializing the environment.", 
 "SE02: Unexpected system exception."], 
@@ -438,9 +438,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -773,14 +774,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1063,14 +1064,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>

--- a/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
+++ b/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\ReframeworkTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9416FC7C-13E9-4FAA-ADCD-EEBCA5873071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125C6215-7F17-4BA0-B088-DE7F3F40D78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="119">
   <si>
     <t>Name</t>
   </si>
@@ -394,6 +394,15 @@
 "BE01: Missing required column in: {0}.", 
 "BE02: Some data isn't correct. Moving to next transaction."],
 "Status": ["OK", "Błąd - wprowadź pozycję ręcznie", "Błąd - brakujące\\niepoprawne dane do wprowadzenia: {0}"]}</t>
+  </si>
+  <si>
+    <t>FileQueueStartDate</t>
+  </si>
+  <si>
+    <t>Data\CurrentQueueStartDate.txt</t>
+  </si>
+  <si>
+    <t>Current Queue start date file path, for reporting purposes.</t>
   </si>
 </sst>
 </file>
@@ -438,10 +447,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -774,14 +782,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1064,14 +1072,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1302,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEB8AB5-FBDE-4982-BC42-69E9F9BF06F4}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="50.77734375" customWidth="1"/>
@@ -1494,6 +1502,17 @@
       </c>
       <c r="C24" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
+++ b/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\ReframeworkTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125C6215-7F17-4BA0-B088-DE7F3F40D78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93F78E7-EF0A-4A57-9FE4-029FFE271A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
+++ b/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\ReframeworkTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6812213-4808-4B77-8DDE-E019B38BCDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8463DE-66C5-4C0B-92CE-59EAEA082CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -283,9 +283,6 @@
     <t>EmailTo_RobotFatal</t>
   </si>
   <si>
-    <t>E-mail to address for process fatal exception.</t>
-  </si>
-  <si>
     <t>EmailSubject_RobotFatal</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
   </si>
   <si>
     <t>Dictionary where key: name of the column used in AddQI Workflow, value: corresponding column name, used in Excel input file.</t>
-  </si>
-  <si>
-    <t>{"Oddzial": "ODDZIAŁ", "Cena": "Column1", "DataOd": "Data od", "Status": "STATUS"}</t>
   </si>
   <si>
     <t>Date range (number of days from now) to check in the Queue for an existing QI. Item with same reference will be skipped. To disable this feature, set the value to 1.</t>
@@ -412,6 +406,12 @@
   </si>
   <si>
     <t>Time after Robot should stop processing due to e.g. server restart, must be text value. To disable this feature set value to: null.</t>
+  </si>
+  <si>
+    <t>{"Status": "STATUS"}</t>
+  </si>
+  <si>
+    <t>E-mail to address for process fatal exception. To disable this feature set value to null.</t>
   </si>
 </sst>
 </file>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -808,7 +808,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
@@ -852,10 +852,10 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
         <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -885,7 +885,7 @@
         <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>72</v>
@@ -910,7 +910,7 @@
         <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -921,7 +921,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -929,10 +929,10 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -943,7 +943,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -951,7 +951,7 @@
         <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
         <v>81</v>
@@ -962,7 +962,7 @@
         <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
         <v>82</v>
@@ -973,54 +973,54 @@
         <v>83</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
         <v>107</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1087,7 +1087,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1098,7 +1098,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
@@ -1142,10 +1142,10 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
         <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1175,7 +1175,7 @@
         <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>72</v>
@@ -1200,7 +1200,7 @@
         <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1211,7 +1211,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1219,10 +1219,10 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1233,7 +1233,7 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1241,7 +1241,7 @@
         <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
         <v>81</v>
@@ -1252,7 +1252,7 @@
         <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
         <v>82</v>
@@ -1266,51 +1266,51 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
         <v>107</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1483,57 +1483,57 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22">
         <v>-1</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
         <v>110</v>
-      </c>
-      <c r="B24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" t="s">
         <v>116</v>
-      </c>
-      <c r="B26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" t="s">
         <v>119</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
+++ b/ReframeworkTemplateC#/Data/Config_Process_Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Inne\04 Programowanie\05 UiPath\02 Projekty\PG-RPA\ReframeworkTemplateC#\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53EDE7C-7C41-4B50-9C8D-DFADB2E8CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA50E9D-5B29-4E50-9BFC-5A0CA986A0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -402,10 +402,19 @@
 Pozdrawiam,&lt;br&gt;Robot&lt;br&gt;Mail: &lt;varEmailAddress&gt;&lt;br&gt;</t>
   </si>
   <si>
+    <t>Data\QueueStartDate.txt</t>
+  </si>
+  <si>
+    <t>{"Col1": "Kolumna1", "Col2": "Kolumna2", "Col3": "Kolumna3", "Status": "STATUS"}</t>
+  </si>
+  <si>
+    <t>Dictionary with mandatory columns when working with an Excel input file, where key: name of the column used in Workflows (QueuePopulate, ExcelGetInputCases, QueueAddItems and SendEmailBusiness), value: corresponding column name from the input file.</t>
+  </si>
+  <si>
     <t>{"TO":{"VShort":2, "Short":4, "Medium":16, "Long":64, "VLong":256},
 "TOms":{"VShort":2000, "Short":4000, "Medium":16000, "Long":64000, "VLong":256000},
 "DEL":{"D1":1, "D2":2, "D3":3, "D4":4, "D6":6, "WaitForQueue":45},
-"RS":{"FoldersCreateDelete":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
+"RS":{"FoldersCreateDelete":{"NR":3, "TS":4}, "ExcelReportProcess":{"NR":3, "TS":6}, "OutlookGetEmails":{"NR":3, "TS":8}, "OutlookSendEmail":{"NR":3, "TS":6}, "AppXYLogin":{"NR":2, "TS":6}, "EdgeLoadingPage":{"NR":9, "TS":3}},
 "SE":["SE00: Critical error while reading Config file.", 
 "SE01: Critical error while initializing the environment."], 
 "AE":["AE00: Unexpected system exception.", 
@@ -413,15 +422,6 @@
 "AE02: Robot couldn't logout from AppXY."], 
 "BE":["BE00: No input data found in: {0} to process."],
 "Status": ["OK", "Błąd - wprowadź pozycję ręcznie."]}</t>
-  </si>
-  <si>
-    <t>Data\QueueStartDate.txt</t>
-  </si>
-  <si>
-    <t>{"Col1": "Kolumna1", "Col2": "Kolumna2", "Col3": "Kolumna3", "Status": "STATUS"}</t>
-  </si>
-  <si>
-    <t>Dictionary with mandatory columns when working with an Excel input file, where key: name of the column used in Workflows (QueuePopulate, ExcelGetInputCases, QueueAddItems and SendEmailBusiness), value: corresponding column name from the input file.</t>
   </si>
 </sst>
 </file>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -480,6 +480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -816,8 +817,8 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>121</v>
+      <c r="B6" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1117,8 +1118,8 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
-        <v>121</v>
+      <c r="B6" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1550,10 +1551,10 @@
         <v>105</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1561,7 +1562,7 @@
         <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
         <v>108</v>
